--- a/output/minute_buy_points/minute_buy_points_20260508.xlsx
+++ b/output/minute_buy_points/minute_buy_points_20260508.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,73 @@
       <c r="O3" t="inlineStr">
         <is>
           <t>603031|5分钟回踩均线启动|2026-05-08 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>603936</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>博敏电子</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>元器件</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>主升趋势类、突破类</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>主升-箱体突破、主升-均线多头排列</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30分钟趋势结构有效</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5分钟回踩均线启动、缠论二买B点、缠论三买B点</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3050460</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.935461533161479</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:39:57</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>603936|5分钟回踩均线启动、缠论二买B点、缠论三买B点|2026-05-08 15:00:00</t>
         </is>
       </c>
     </row>

--- a/output/minute_buy_points/minute_buy_points_20260508.xlsx
+++ b/output/minute_buy_points/minute_buy_points_20260508.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,73 +636,6 @@
       <c r="O3" t="inlineStr">
         <is>
           <t>603031|5分钟回踩均线启动|2026-05-08 15:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>603936</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>博敏电子</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-08 15:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>元器件</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>主升趋势类、突破类</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>主升-箱体突破、主升-均线多头排列</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30分钟趋势结构有效</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5分钟回踩均线启动、缠论二买B点、缠论三买B点</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3050460</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.935461533161479</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-05-08 22:39:57</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>603936|5分钟回踩均线启动、缠论二买B点、缠论三买B点|2026-05-08 15:00:00</t>
         </is>
       </c>
     </row>
